--- a/ai_model/attendance_log.xlsx
+++ b/ai_model/attendance_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,60 @@
         </is>
       </c>
       <c r="E4" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>30409161402435</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Mohamed Adel</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>12:40:07</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>23230035</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>zeyad wael</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>13:09:57</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Present</t>
         </is>

--- a/ai_model/attendance_log.xlsx
+++ b/ai_model/attendance_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,6 +578,114 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>30409161402435</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mohamed Adel</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>01:00:07</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>23230035</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>zeyad wael</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>01:42:35</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>23230011</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>esraa ahdy</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>12:44:44</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>23230099</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ahmed abdelhamed</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>12:45:07</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ai_model/attendance_log.xlsx
+++ b/ai_model/attendance_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,6 +686,87 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>30409161402435</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mohamed Adel</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>01:35:12</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>30409161402435</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mohamed Adel</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>17:12:16</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>30409161402435</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mohamed Adel</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>17:32:14</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
